--- a/data/trade_analysis/league_rosters_2026_wk3.xlsx
+++ b/data/trade_analysis/league_rosters_2026_wk3.xlsx
@@ -7,18 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tush Push Director 🍑" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Third Down and Long Story" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gridiron Grace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sacks and the City" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hurts Locker Room Talk" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Say Cheese 🧀💚🧀" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="It's Miller Time" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flock Around and Find Out" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Immaculate Concepcion" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hurts so Good " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bianca" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="michelle’s boy toys " sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Junya Ettlinger's First Team" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ler and Order" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunks of Hanet " sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serving Punt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jockstrap jubilee " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Natural rack" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sacks and the City" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Closed " sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big Ballsy Bozos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hall Pass" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,24 +477,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Jalen Hurts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB17</t>
+          <t>QB3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB2</t>
+          <t>QB9</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27.76</v>
+        <v>20.44</v>
       </c>
       <c r="F2" t="n">
-        <v>16.95</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="3">
@@ -507,52 +505,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Jared Goff</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB33</t>
+          <t>QB11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB13</t>
+          <t>QB5</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16.86</v>
+        <v>23.11</v>
       </c>
       <c r="F3" t="n">
-        <v>13.88</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jaxson Dart</t>
+          <t>Bijan Robinson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>RB2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>QB22</t>
+          <t>RB7</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>13.7</v>
+        <v>18.45</v>
       </c>
       <c r="F4" t="n">
-        <v>18.16</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="5">
@@ -563,24 +561,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Breece Hall</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB7</t>
+          <t>RB16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB16</t>
+          <t>RB11</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>15.25</v>
       </c>
       <c r="F5" t="n">
-        <v>17.63</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="6">
@@ -591,24 +589,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cam Skattebo</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB20</t>
+          <t>RB33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB20</t>
+          <t>RB24</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>12.41</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -619,80 +617,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rico Dowdle</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB31</t>
+          <t>RB41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB48</t>
+          <t>RB38</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="F7" t="n">
-        <v>10.83</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WR3</t>
+          <t>RB43</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WR2</t>
+          <t>RB36</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31.95</v>
+        <v>11.9</v>
       </c>
       <c r="F8" t="n">
-        <v>20.36</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Kaelon Black</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR6</t>
+          <t>RB45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR3</t>
+          <t>RB46</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25.4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>15.98</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="10">
@@ -703,24 +701,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Drake London</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR30</t>
+          <t>WR12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR5</t>
+          <t>WR50</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24.2</v>
+        <v>5.7</v>
       </c>
       <c r="F10" t="n">
-        <v>14.09</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="11">
@@ -731,24 +729,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carnell Tate</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR36</t>
+          <t>WR18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR58</t>
+          <t>WR4</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.75</v>
+        <v>20.9</v>
       </c>
       <c r="F11" t="n">
-        <v>11.77</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="12">
@@ -759,164 +757,192 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR46</t>
+          <t>WR19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR53</t>
+          <t>WR22</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.2</v>
+        <v>10.3</v>
       </c>
       <c r="F12" t="n">
-        <v>11.34</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tyler Warren</t>
+          <t>Ladd McConkey</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TE5</t>
+          <t>WR21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TE9</t>
+          <t>WR19</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.35</v>
+        <v>10.85</v>
       </c>
       <c r="F13" t="n">
-        <v>12.05</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>Josh Downs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TE30</t>
+          <t>WR31</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TE11</t>
+          <t>WR37</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="F14" t="n">
-        <v>8.16</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D/ST</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bengals D/ST</t>
+          <t>Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>WR42</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>D/ST1</t>
+          <t>WR54</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="F15" t="n">
-        <v>5.62</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cairo Santos</t>
+          <t>Sam LaPorta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K10</t>
+          <t>TE6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>K16</t>
+          <t>TE7</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>10.75</v>
       </c>
       <c r="F16" t="n">
-        <v>8.119999999999999</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>D/ST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Steelers D/ST</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(n/a)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>D/ST1</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Harrison Mevis</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>K11</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>K31</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8.960000000000001</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Brandon Aubrey</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.93</v>
       </c>
     </row>
   </sheetData>
@@ -973,24 +999,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Drake Maye</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB20</t>
+          <t>QB4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB25</t>
+          <t>QB30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11.91</v>
+        <v>8.92</v>
       </c>
       <c r="F2" t="n">
-        <v>16.56</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="3">
@@ -1001,24 +1027,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB24</t>
+          <t>QB7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB38</t>
+          <t>QB4</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.52</v>
+        <v>24.79</v>
       </c>
       <c r="F3" t="n">
-        <v>15.94</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="4">
@@ -1029,24 +1055,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Christian McCaffrey</t>
+          <t>James Cook III</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB5</t>
+          <t>RB6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RB9</t>
+          <t>RB12</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18.2</v>
+        <v>14.4</v>
       </c>
       <c r="F4" t="n">
-        <v>19.52</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="5">
@@ -1057,24 +1083,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>RB17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>RB13</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RB13</t>
-        </is>
-      </c>
       <c r="E5" t="n">
-        <v>16.1</v>
+        <v>14.35</v>
       </c>
       <c r="F5" t="n">
-        <v>15.77</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="6">
@@ -1085,24 +1111,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB25</t>
+          <t>RB36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB28</t>
+          <t>RB43</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9.050000000000001</v>
+        <v>5.45</v>
       </c>
       <c r="F6" t="n">
-        <v>12.3</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="7">
@@ -1113,24 +1139,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB47</t>
+          <t>RB37</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB35</t>
+          <t>RB54</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="F7" t="n">
-        <v>8.44</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1141,24 +1167,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WR10</t>
+          <t>WR7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WR18</t>
+          <t>WR8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>17.1</v>
       </c>
       <c r="F8" t="n">
-        <v>16.33</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="9">
@@ -1169,24 +1195,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mike Evans</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR24</t>
+          <t>WR16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR22</t>
+          <t>WR15</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12.65</v>
+        <v>12.55</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="10">
@@ -1197,24 +1223,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr.</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR38</t>
+          <t>WR29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR24</t>
+          <t>WR57</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12.25</v>
+        <v>5.4</v>
       </c>
       <c r="F10" t="n">
-        <v>11.76</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1225,24 +1251,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>Deebo Samuel Sr.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR43</t>
+          <t>WR38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR73</t>
+          <t>WR24</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.35</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>8.01</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="12">
@@ -1253,24 +1279,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Keenan Allen</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR61</t>
+          <t>WR43</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR73</t>
+          <t>WR78</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.35</v>
+        <v>3.85</v>
       </c>
       <c r="F12" t="n">
-        <v>9.01</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="13">
@@ -1281,24 +1307,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Travis Kelce</t>
+          <t>Tyler Warren</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>TE5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>TE10</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TE4</t>
-        </is>
-      </c>
       <c r="E13" t="n">
-        <v>17.6</v>
+        <v>10.1</v>
       </c>
       <c r="F13" t="n">
-        <v>12.31</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="14">
@@ -1309,52 +1335,52 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TE14</t>
+          <t>TE10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TE7</t>
+          <t>TE4</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12.55</v>
+        <v>14.6</v>
       </c>
       <c r="F14" t="n">
-        <v>10.86</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>D/ST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Texans D/ST</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE26</t>
+          <t>(n/a)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE31</t>
+          <t>D/ST26</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="F15" t="n">
-        <v>6.31</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="16">
@@ -1365,7 +1391,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Patriots D/ST</t>
+          <t>Chargers D/ST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1375,14 +1401,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST1</t>
+          <t>D/ST24</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.5</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>5.26</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="17">
@@ -1393,12 +1419,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jake Elliott</t>
+          <t>Jason Myers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K21</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1410,1051 +1436,7 @@
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>8.050000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FP Rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ESPN Rank</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Actual PPG</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Proj PPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>QB6</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>QB20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18.24</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Patrick Mahomes</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>QB9</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>QB3</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="F3" t="n">
-        <v>18.28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bijan Robinson</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RB2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RB7</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>20.06</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bhayshul Tuten</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>RB21</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RB19</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
-        <v>11.09</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RB41</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RB40</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kaelon Black</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RB45</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RB48</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Brian Robinson Jr.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>RB55</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RB45</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.98</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DJ Moore</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>WR23</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>WR34</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="F9" t="n">
-        <v>13.23</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>A.J. Brown</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>WR26</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>WR100</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>15.04</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Luther Burden III</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>WR27</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>WR48</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Chris Godwin Jr.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>WR34</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>WR40</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.19</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Brian Thomas Jr.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>WR42</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>WR55</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10.82</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Adonai Mitchell</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>WR53</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>WR32</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10.46</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TE2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>14.47</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Oronde Gadsden</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TE22</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TE20</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8.23</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>D/ST</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Seahawks D/ST</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>(n/a)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>D/ST5</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>12</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tyler Loop</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K8</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FP Rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ESPN Rank</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Actual PPG</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Proj PPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bo Nix</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>QB16</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>QB29</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="F2" t="n">
-        <v>17.45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>C.J. Stroud</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>QB21</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>QB14</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="F3" t="n">
-        <v>15.61</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Derrick Henry</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RB9</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RB4</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>17.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Saquon Barkley</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>RB10</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RB42</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>18.09</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RB29</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RB30</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Jonah Coleman</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RB42</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RB31</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>RB43</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RB43</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10.13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jaylen Waddle</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>WR13</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>WR26</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>13.28</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Terry McLaurin</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>WR28</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>WR76</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Denzel Boston</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>WR41</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>WR12</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10.92</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Makai Lemon</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>WR47</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>WR106</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5.73</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Marvin Harrison Jr.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>WR51</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>WR107</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Xavier Worthy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>WR54</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>WR38</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="F14" t="n">
-        <v>11.01</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Harold Fannin Jr.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TE8</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TE21</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="F15" t="n">
-        <v>9.48</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dalton Schultz</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TE15</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TE5</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="F16" t="n">
-        <v>9.31</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>D/ST</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Texans D/ST</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>(n/a)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>D/ST26</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Evan McPherson</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K7</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.44</v>
+        <v>9.27</v>
       </c>
     </row>
   </sheetData>
@@ -2468,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2511,24 +1493,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trevor Lawrence</t>
+          <t>Caleb Williams</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB5</t>
+          <t>QB10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB17</t>
+          <t>QB7</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16.13</v>
+        <v>22.49</v>
       </c>
       <c r="F2" t="n">
-        <v>17.76</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="3">
@@ -2539,24 +1521,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB14</t>
+          <t>QB17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB6</t>
+          <t>QB2</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22.79</v>
+        <v>27.76</v>
       </c>
       <c r="F3" t="n">
-        <v>18.14</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="4">
@@ -2567,24 +1549,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>De'Von Achane</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB12</t>
+          <t>RB8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RB21</t>
+          <t>RB6</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.45</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>19.47</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="5">
@@ -2595,24 +1577,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David Montgomery</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB19</t>
+          <t>RB13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB11</t>
+          <t>RB14</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16.65</v>
+        <v>14.1</v>
       </c>
       <c r="F5" t="n">
-        <v>11.7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="6">
@@ -2623,24 +1605,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB27</t>
+          <t>RB23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB25</t>
+          <t>RB30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="F6" t="n">
-        <v>12.97</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2651,24 +1633,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Kyle Monangai</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB28</t>
+          <t>RB32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB8</t>
+          <t>RB16</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.05</v>
+        <v>13.1</v>
       </c>
       <c r="F7" t="n">
-        <v>14.09</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2679,52 +1661,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tank Bigsby</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB51</t>
+          <t>RB48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RB41</t>
+          <t>RB37</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
       <c r="F8" t="n">
-        <v>3.28</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Dylan Sampson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR7</t>
+          <t>RB62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR8</t>
+          <t>RB95</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19.85</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>18.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2735,24 +1717,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR19</t>
+          <t>WR1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR20</t>
+          <t>WR14</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="F10" t="n">
-        <v>14.52</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="11">
@@ -2763,24 +1745,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Parker Washington</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR39</t>
+          <t>WR15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR86</t>
+          <t>WR11</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>15.05</v>
       </c>
       <c r="F11" t="n">
-        <v>11.13</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="12">
@@ -2791,164 +1773,192 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Emeka Egbuka</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR73</t>
+          <t>WR20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR28</t>
+          <t>WR33</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.26</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Brenton Strange</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TE18</t>
+          <t>WR36</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TE24</t>
+          <t>WR61</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>8.02</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hunter Henry</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TE19</t>
+          <t>WR41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TE29</t>
+          <t>WR10</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.3</v>
+        <v>15.45</v>
       </c>
       <c r="F14" t="n">
-        <v>9.470000000000001</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE21</t>
+          <t>WR47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE15</t>
+          <t>WR113</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.75</v>
+        <v>1.2</v>
       </c>
       <c r="F15" t="n">
-        <v>9.279999999999999</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D/ST</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>49ers D/ST</t>
+          <t>Kyle Pitts Sr.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>TE12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST8</t>
+          <t>TE55</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>5.4</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>D/ST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lions D/ST</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(n/a)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>D/ST31</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Trey Smack</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>K19</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>K4</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8.76</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Harrison Butker</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>K13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.779999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2962,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3005,24 +2015,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Caleb Williams</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB10</t>
+          <t>QB6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB7</t>
+          <t>QB20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22.49</v>
+        <v>15.17</v>
       </c>
       <c r="F2" t="n">
-        <v>17.13</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="3">
@@ -3033,24 +2043,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Jordan Love</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB25</t>
+          <t>QB13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB24</t>
+          <t>QB15</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12.44</v>
+        <v>16.64</v>
       </c>
       <c r="F3" t="n">
-        <v>14.7</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="4">
@@ -3061,24 +2071,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>RB3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>RB4</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RB1</t>
-        </is>
-      </c>
       <c r="E4" t="n">
-        <v>28.95</v>
+        <v>25.4</v>
       </c>
       <c r="F4" t="n">
-        <v>19.56</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="5">
@@ -3089,24 +2099,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Breece Hall</t>
+          <t>Omarion Hampton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB16</t>
+          <t>RB11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB10</t>
+          <t>RB18</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>12.4</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="6">
@@ -3117,24 +2127,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>D'Andre Swift</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB18</t>
+          <t>RB14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB11</t>
+          <t>RB5</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.65</v>
+        <v>21.15</v>
       </c>
       <c r="F6" t="n">
-        <v>16.42</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="7">
@@ -3145,24 +2155,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rachaad White</t>
+          <t>Josh Jacobs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB39</t>
+          <t>RB38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB26</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>9.630000000000001</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="8">
@@ -3173,24 +2183,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB89</t>
+          <t>RB42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>RB31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="9">
@@ -3201,24 +2211,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Chris Olave</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>WR6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>WR4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>WR67</t>
-        </is>
-      </c>
       <c r="E9" t="n">
-        <v>12.4</v>
+        <v>20.9</v>
       </c>
       <c r="F9" t="n">
-        <v>22.49</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="10">
@@ -3239,14 +2249,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR55</t>
+          <t>WR60</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="F10" t="n">
-        <v>15.37</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="11">
@@ -3257,24 +2267,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Josh Downs</t>
+          <t>Rome Odunze</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR31</t>
+          <t>WR32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR35</t>
+          <t>WR47</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.949999999999999</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>10.25</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="12">
@@ -3285,24 +2295,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jordan Addison</t>
+          <t>DK Metcalf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR49</t>
+          <t>WR35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR109</t>
+          <t>WR58</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.05</v>
+        <v>5.35</v>
       </c>
       <c r="F12" t="n">
-        <v>10.76</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="13">
@@ -3313,52 +2323,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr.</t>
+          <t>Jakobi Meyers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WR52</t>
+          <t>WR48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WR85</t>
+          <t>WR40</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.25</v>
       </c>
       <c r="F13" t="n">
-        <v>11.89</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WR71</t>
+          <t>TE7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WR63</t>
+          <t>TE25</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
       <c r="F14" t="n">
-        <v>3.85</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="15">
@@ -3369,108 +2379,80 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid</t>
+          <t>Juwan Johnson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE3</t>
+          <t>TE13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE2</t>
+          <t>TE7</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20.25</v>
+        <v>10.75</v>
       </c>
       <c r="F15" t="n">
-        <v>11.44</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>D/ST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Colston Loveland</t>
+          <t>Eagles D/ST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TE4</t>
+          <t>(n/a)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TE77</t>
+          <t>D/ST19</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.65</v>
+        <v>4.5</v>
       </c>
       <c r="F16" t="n">
-        <v>9.869999999999999</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D/ST</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jets D/ST</t>
+          <t>Cam Little</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>D/ST7</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>9.5</v>
       </c>
       <c r="F17" t="n">
-        <v>5.47</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Jason Myers</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K4</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K20</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>9.27</v>
+        <v>8.59</v>
       </c>
     </row>
   </sheetData>
@@ -3527,24 +2509,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Josh Allen</t>
+          <t>Trevor Lawrence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB1</t>
+          <t>QB5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB1</t>
+          <t>QB17</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38.24</v>
+        <v>16.13</v>
       </c>
       <c r="F2" t="n">
-        <v>22.89</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="3">
@@ -3555,24 +2537,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Justin Herbert</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB15</t>
+          <t>QB12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB19</t>
+          <t>QB27</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15.54</v>
+        <v>10.57</v>
       </c>
       <c r="F3" t="n">
-        <v>17.67</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="4">
@@ -3583,24 +2565,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jeremiyah Love</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB15</t>
+          <t>RB1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RB23</t>
+          <t>RB2</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.25</v>
+        <v>25.7</v>
       </c>
       <c r="F4" t="n">
-        <v>13.36</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="5">
@@ -3611,24 +2593,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jadarian Price</t>
+          <t>Jeremiyah Love</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB24</t>
+          <t>RB15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB38</t>
+          <t>RB23</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>11.87</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="6">
@@ -3639,24 +2621,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Cam Skattebo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB34</t>
+          <t>RB20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB57</t>
+          <t>RB20</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.6</v>
+        <v>10.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12.08</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="7">
@@ -3667,80 +2649,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB44</t>
+          <t>RB27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB37</t>
+          <t>RB26</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.45</v>
+        <v>8.25</v>
       </c>
       <c r="F7" t="n">
-        <v>7.94</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB52</t>
+          <t>WR10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RB57</t>
+          <t>WR18</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.2</v>
+        <v>23.5</v>
       </c>
       <c r="F8" t="n">
-        <v>9.4</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Mike Evans</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RB61</t>
+          <t>WR24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RB50</t>
+          <t>WR20</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.75</v>
+        <v>10.4</v>
       </c>
       <c r="F9" t="n">
-        <v>7.84</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="10">
@@ -3751,24 +2733,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>A.J. Brown</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR2</t>
+          <t>WR26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR1</t>
+          <t>WR102</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34.35</v>
+        <v>4.1</v>
       </c>
       <c r="F10" t="n">
-        <v>20.32</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="11">
@@ -3779,24 +2761,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR8</t>
+          <t>WR34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR45</t>
+          <t>WR43</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="n">
-        <v>13.86</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="12">
@@ -3807,24 +2789,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Davante Adams</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR25</t>
+          <t>WR37</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR7</t>
+          <t>WR23</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22.55</v>
+        <v>10.15</v>
       </c>
       <c r="F12" t="n">
-        <v>14.59</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="13">
@@ -3835,24 +2817,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Khalil Shakir</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WR50</t>
+          <t>WR62</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WR45</t>
+          <t>WR89</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.9</v>
+        <v>3.15</v>
       </c>
       <c r="F13" t="n">
-        <v>10.17</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="14">
@@ -3863,24 +2845,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Juwan Johnson</t>
+          <t>George Kittle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>TE9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>TE13</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TE8</t>
-        </is>
-      </c>
       <c r="E14" t="n">
-        <v>12.5</v>
+        <v>9.1</v>
       </c>
       <c r="F14" t="n">
-        <v>9.18</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="15">
@@ -3891,24 +2873,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mark Andrews</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE16</t>
+          <t>TE19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE14</t>
+          <t>TE33</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.9</v>
+        <v>4.8</v>
       </c>
       <c r="F15" t="n">
-        <v>9.960000000000001</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="16">
@@ -3919,7 +2901,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Buccaneers D/ST</t>
+          <t>Seahawks D/ST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3929,14 +2911,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST14</t>
+          <t>D/ST5</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>4.25</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="17">
@@ -3947,24 +2929,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jake Bates</t>
+          <t>Eddy Pineiro</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K12</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>K20</t>
+          <t>K18</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="n">
-        <v>8.69</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4021,52 +3003,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jalen Hurts</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB3</t>
+          <t>QB14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB9</t>
+          <t>QB6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20.44</v>
+        <v>22.79</v>
       </c>
       <c r="F2" t="n">
-        <v>19.23</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>De'Von Achane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB11</t>
+          <t>RB12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB5</t>
+          <t>RB22</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23.11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>17.03</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="4">
@@ -4077,24 +3059,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr.</t>
+          <t>David Montgomery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB22</t>
+          <t>RB19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RB22</t>
+          <t>RB10</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.95</v>
+        <v>15.4</v>
       </c>
       <c r="F4" t="n">
-        <v>11.72</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="5">
@@ -4105,24 +3087,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB26</t>
+          <t>RB22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB29</t>
+          <t>RB24</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>12.46</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="6">
@@ -4133,24 +3115,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kyle Monangai</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB32</t>
+          <t>RB29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB17</t>
+          <t>RB27</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14.1</v>
+        <v>7.55</v>
       </c>
       <c r="F6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -4161,24 +3143,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB63</t>
+          <t>RB30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB46</t>
+          <t>RB21</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.6</v>
+        <v>10.25</v>
       </c>
       <c r="F7" t="n">
-        <v>4.91</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="8">
@@ -4189,24 +3171,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WR5</t>
+          <t>WR3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WR4</t>
+          <t>WR2</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25.35</v>
+        <v>27.2</v>
       </c>
       <c r="F8" t="n">
-        <v>17.38</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="9">
@@ -4217,24 +3199,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>DeVonta Smith</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR16</t>
+          <t>WR9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR14</t>
+          <t>WR12</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.3</v>
+        <v>14.75</v>
       </c>
       <c r="F9" t="n">
-        <v>14.45</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="10">
@@ -4245,24 +3227,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rome Odunze</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR32</t>
+          <t>WR13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR52</t>
+          <t>WR28</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.25</v>
+        <v>9.25</v>
       </c>
       <c r="F10" t="n">
-        <v>10.44</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="11">
@@ -4273,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jakobi Meyers</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR48</t>
+          <t>WR30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR43</t>
+          <t>WR6</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>20.2</v>
       </c>
       <c r="F11" t="n">
-        <v>9.44</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="12">
@@ -4301,24 +3283,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR58</t>
+          <t>WR33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR78</t>
+          <t>WR9</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.9</v>
+        <v>16.35</v>
       </c>
       <c r="F12" t="n">
-        <v>6.64</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -4329,24 +3311,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jayden Reed</t>
+          <t>Quentin Johnston</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WR70</t>
+          <t>WR44</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WR95</t>
+          <t>WR97</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="F13" t="n">
-        <v>9.960000000000001</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -4357,24 +3339,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>TE14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>TE6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TE6</t>
-        </is>
-      </c>
       <c r="E14" t="n">
-        <v>13.5</v>
+        <v>11.3</v>
       </c>
       <c r="F14" t="n">
-        <v>11.49</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="15">
@@ -4385,24 +3367,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Dalton Schultz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE11</t>
+          <t>TE15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE3</t>
+          <t>TE5</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18.05</v>
+        <v>12.75</v>
       </c>
       <c r="F15" t="n">
-        <v>12.72</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="16">
@@ -4413,7 +3395,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Broncos D/ST</t>
+          <t>Browns D/ST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4423,14 +3405,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST16</t>
+          <t>D/ST24</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>6.18</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="17">
@@ -4441,24 +3423,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ka'imi Fairbairn</t>
+          <t>Cairo Santos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>K18</t>
+          <t>K16</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
-        <v>9.300000000000001</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4472,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4515,24 +3497,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Drake Maye</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB4</t>
+          <t>QB9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB30</t>
+          <t>QB3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8.92</v>
+        <v>25.32</v>
       </c>
       <c r="F2" t="n">
-        <v>19.16</v>
+        <v>18.28</v>
       </c>
     </row>
     <row r="3">
@@ -4543,24 +3525,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Justin Herbert</t>
+          <t>Jayden Daniels</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB12</t>
+          <t>QB23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB27</t>
+          <t>QB16</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.57</v>
+        <v>16.2</v>
       </c>
       <c r="F3" t="n">
-        <v>15.82</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="4">
@@ -4571,24 +3553,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian McCaffrey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB3</t>
+          <t>RB5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RB3</t>
+          <t>RB9</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27.15</v>
+        <v>15.95</v>
       </c>
       <c r="F4" t="n">
-        <v>21.4</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="5">
@@ -4599,24 +3581,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Omarion Hampton</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB11</t>
+          <t>RB10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB18</t>
+          <t>RB41</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12.9</v>
+        <v>5.5</v>
       </c>
       <c r="F5" t="n">
-        <v>14.56</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="6">
@@ -4627,24 +3609,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Bhayshul Tuten</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB35</t>
+          <t>RB21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB51</t>
+          <t>RB19</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.65</v>
+        <v>11.25</v>
       </c>
       <c r="F6" t="n">
-        <v>7.03</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="7">
@@ -4655,24 +3637,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tyjae Spears</t>
+          <t>Rico Dowdle</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB48</t>
+          <t>RB31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB36</t>
+          <t>RB51</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.7</v>
+        <v>4.25</v>
       </c>
       <c r="F7" t="n">
-        <v>9.609999999999999</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="8">
@@ -4683,24 +3665,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WR17</t>
+          <t>WR8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WR25</t>
+          <t>WR51</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11.7</v>
+        <v>5.65</v>
       </c>
       <c r="F8" t="n">
-        <v>13.45</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="9">
@@ -4711,24 +3693,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rashee Rice</t>
+          <t>DJ Moore</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR22</t>
+          <t>WR23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR27</t>
+          <t>WR29</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>12.34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -4739,24 +3721,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Davante Adams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR35</t>
+          <t>WR25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR50</t>
+          <t>WR7</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.35</v>
+        <v>19.8</v>
       </c>
       <c r="F10" t="n">
-        <v>11.05</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="11">
@@ -4767,24 +3749,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR37</t>
+          <t>WR45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR22</t>
+          <t>WR53</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.65</v>
+        <v>5.55</v>
       </c>
       <c r="F11" t="n">
-        <v>11.09</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
@@ -4795,24 +3777,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR45</t>
+          <t>WR64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR64</t>
+          <t>WR13</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.3</v>
+        <v>12.65</v>
       </c>
       <c r="F12" t="n">
-        <v>8.67</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="13">
@@ -4823,52 +3805,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Jayden Reed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WR79</t>
+          <t>WR70</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WR140</t>
+          <t>WR100</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="F13" t="n">
-        <v>6.02</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TE7</t>
+          <t>WR115</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TE26</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>10.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4879,80 +3861,108 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE24</t>
+          <t>TE1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE19</t>
+          <t>TE2</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.55</v>
+        <v>17.05</v>
       </c>
       <c r="F15" t="n">
-        <v>7.24</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D/ST</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Steelers D/ST</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>TE11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST1</t>
+          <t>TE3</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.5</v>
+        <v>14.8</v>
       </c>
       <c r="F16" t="n">
-        <v>5.84</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>D/ST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Broncos D/ST</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(n/a)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>D/ST16</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Brandon Aubrey</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>9.93</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ka'imi Fairbairn</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>K18</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4966,7 +3976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5009,24 +4019,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Lamar Jackson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB13</t>
+          <t>QB2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB15</t>
+          <t>QB10</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16.64</v>
+        <v>19.88</v>
       </c>
       <c r="F2" t="n">
-        <v>16.14</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="3">
@@ -5037,24 +4047,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jayden Daniels</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB23</t>
+          <t>QB15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB16</t>
+          <t>QB19</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16.2</v>
+        <v>15.54</v>
       </c>
       <c r="F3" t="n">
-        <v>19.25</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="4">
@@ -5065,24 +4075,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>RB4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>RB1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RB2</t>
-        </is>
-      </c>
       <c r="E4" t="n">
-        <v>28.45</v>
+        <v>26.7</v>
       </c>
       <c r="F4" t="n">
-        <v>25.37</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="5">
@@ -5093,24 +4103,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson</t>
+          <t>Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB23</t>
+          <t>RB25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB34</t>
+          <t>RB28</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13.6</v>
+        <v>7.55</v>
       </c>
       <c r="F5" t="n">
-        <v>10.85</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="6">
@@ -5121,24 +4131,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr.</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB30</t>
+          <t>RB34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB23</t>
+          <t>RB53</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.25</v>
+        <v>3.6</v>
       </c>
       <c r="F6" t="n">
-        <v>11.51</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="7">
@@ -5149,24 +4159,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB33</t>
+          <t>RB35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB27</t>
+          <t>RB52</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9.199999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="F7" t="n">
-        <v>9.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5177,52 +4187,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kenny Gainwell</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB40</t>
+          <t>RB44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RB56</t>
+          <t>RB42</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.65</v>
+        <v>5.45</v>
       </c>
       <c r="F8" t="n">
-        <v>7.91</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Drake London</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR12</t>
+          <t>RB89</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR53</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5233,24 +4243,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Parker Washington</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR15</t>
+          <t>WR2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR10</t>
+          <t>WR1</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.05</v>
+        <v>30.1</v>
       </c>
       <c r="F10" t="n">
-        <v>15.27</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="11">
@@ -5261,24 +4271,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ladd McConkey</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR21</t>
+          <t>WR17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR19</t>
+          <t>WR25</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>12.83</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="12">
@@ -5289,24 +4299,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Luther Burden III</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR29</t>
+          <t>WR27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR57</t>
+          <t>WR48</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.9</v>
+        <v>5.85</v>
       </c>
       <c r="F12" t="n">
-        <v>11.16</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="13">
@@ -5317,52 +4327,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WR33</t>
+          <t>WR40</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WR9</t>
+          <t>WR54</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>18.6</v>
+        <v>5.5</v>
       </c>
       <c r="F13" t="n">
-        <v>11.04</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TE1</t>
+          <t>WR52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TE1</t>
+          <t>WR84</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21.3</v>
+        <v>7.3</v>
       </c>
       <c r="F14" t="n">
-        <v>16.5</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="15">
@@ -5373,80 +4383,108 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Brock Bowers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE20</t>
+          <t>TE2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE17</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>8.34</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D/ST</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lions D/ST</t>
+          <t>Dalton Kincaid</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>TE3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST31</t>
+          <t>TE1</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>17.25</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>D/ST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rams D/ST</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(n/a)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>D/ST14</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Cam Little</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8.59</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Chris Boswell</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>K16</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>K28</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.07</v>
       </c>
     </row>
   </sheetData>
@@ -5460,7 +4498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5531,24 +4569,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB19</t>
+          <t>QB16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB51</t>
+          <t>QB29</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-0.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>18.52</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="4">
@@ -5559,24 +4597,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB8</t>
+          <t>RB7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RB6</t>
+          <t>RB17</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21.5</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>18.05</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="5">
@@ -5587,24 +4625,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D'Andre Swift</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB14</t>
+          <t>RB26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB5</t>
+          <t>RB31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22.65</v>
+        <v>6.65</v>
       </c>
       <c r="F5" t="n">
-        <v>13.12</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="6">
@@ -5615,24 +4653,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Rachaad White</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB17</t>
+          <t>RB39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB14</t>
+          <t>RB29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15.6</v>
+        <v>7.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.53</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -5643,24 +4681,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Mike Washington Jr.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB54</t>
+          <t>RB46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>RB63</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="F7" t="n">
-        <v>12.62</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="8">
@@ -5671,24 +4709,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WR1</t>
+          <t>WR4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WR15</t>
+          <t>WR62</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14.85</v>
+        <v>9.9</v>
       </c>
       <c r="F8" t="n">
-        <v>20.03</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="9">
@@ -5699,24 +4737,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Nico Collins</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR18</t>
+          <t>WR11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR6</t>
+          <t>WR32</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23.4</v>
+        <v>17.7</v>
       </c>
       <c r="F9" t="n">
-        <v>13.68</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="10">
@@ -5727,24 +4765,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Emeka Egbuka</t>
+          <t>Terry McLaurin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR20</t>
+          <t>WR28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR31</t>
+          <t>WR74</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.8</v>
+        <v>4.2</v>
       </c>
       <c r="F10" t="n">
-        <v>12.92</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="11">
@@ -5755,80 +4793,80 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Courtland Sutton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR59</t>
+          <t>WR39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR38</t>
+          <t>WR90</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.15</v>
+        <v>3.05</v>
       </c>
       <c r="F11" t="n">
-        <v>9.32</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr.</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TE12</t>
+          <t>WR46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TE57</t>
+          <t>WR56</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.25</v>
+        <v>5.45</v>
       </c>
       <c r="F12" t="n">
-        <v>9.91</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TE17</t>
+          <t>WR55</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TE12</t>
+          <t>WR66</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11.45</v>
+        <v>4.85</v>
       </c>
       <c r="F13" t="n">
-        <v>8.720000000000001</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="14">
@@ -5839,52 +4877,52 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zach Ertz</t>
+          <t>Colston Loveland</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>TE4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TE76</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>3.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D/ST</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eagles D/ST</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>TE17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>D/ST19</t>
+          <t>TE11</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.5</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>5.49</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="16">
@@ -5895,7 +4933,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vikings D/ST</t>
+          <t>Patriots D/ST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5905,14 +4943,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST6</t>
+          <t>D/ST1</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="F16" t="n">
-        <v>6.01</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="17">
@@ -5923,52 +4961,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cameron Dicker</t>
+          <t>Harrison Mevis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>K11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>K32</t>
+          <t>K31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>8.859999999999999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Chase McLaughlin</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K9</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K2</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.529999999999999</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5982,7 +4992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6025,24 +5035,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lamar Jackson</t>
+          <t>Josh Allen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QB2</t>
+          <t>QB1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QB10</t>
+          <t>QB1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19.88</v>
+        <v>38.24</v>
       </c>
       <c r="F2" t="n">
-        <v>20.81</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="3">
@@ -6053,24 +5063,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>QB7</t>
+          <t>QB21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QB4</t>
+          <t>QB14</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24.79</v>
+        <v>16.74</v>
       </c>
       <c r="F3" t="n">
-        <v>18.9</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="4">
@@ -6081,24 +5091,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>James Cook III</t>
+          <t>Derrick Henry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB6</t>
+          <t>RB9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RB15</t>
+          <t>RB3</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15.4</v>
+        <v>25.5</v>
       </c>
       <c r="F4" t="n">
-        <v>16.77</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="5">
@@ -6109,24 +5119,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RB36</t>
+          <t>RB18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RB43</t>
+          <t>RB15</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.95</v>
+        <v>13.9</v>
       </c>
       <c r="F5" t="n">
-        <v>10.27</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="6">
@@ -6137,24 +5147,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Jadarian Price</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB37</t>
+          <t>RB24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RB53</t>
+          <t>RB39</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8.1</v>
+        <v>5.65</v>
       </c>
       <c r="F6" t="n">
-        <v>10.48</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="7">
@@ -6165,24 +5175,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RB62</t>
+          <t>RB28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB95</t>
+          <t>RB8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="8">
@@ -6193,24 +5203,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>Kenny Gainwell</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB69</t>
+          <t>RB40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RB55</t>
+          <t>RB60</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="F8" t="n">
-        <v>6.56</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="9">
@@ -6221,24 +5231,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DeVonta Smith</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WR9</t>
+          <t>WR5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR11</t>
+          <t>WR3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>22.1</v>
       </c>
       <c r="F9" t="n">
-        <v>15.41</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="10">
@@ -6249,24 +5259,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nico Collins</t>
+          <t>Rashee Rice</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WR11</t>
+          <t>WR22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WR33</t>
+          <t>WR26</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21.2</v>
+        <v>9.6</v>
       </c>
       <c r="F10" t="n">
-        <v>16.57</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="11">
@@ -6277,24 +5287,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Jordan Addison</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WR40</t>
+          <t>WR49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR43</t>
+          <t>WR111</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>1.55</v>
       </c>
       <c r="F11" t="n">
-        <v>10.49</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -6305,24 +5315,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WR56</t>
+          <t>WR51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR16</t>
+          <t>WR103</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.85</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="n">
-        <v>9.279999999999999</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="13">
@@ -6333,52 +5343,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WR64</t>
+          <t>WR54</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WR13</t>
+          <t>WR41</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15.65</v>
+        <v>7.15</v>
       </c>
       <c r="F13" t="n">
-        <v>7.92</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Travis Hunter</t>
+          <t>Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WR89</t>
+          <t>TE8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>WR122</t>
+          <t>TE24</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="F14" t="n">
-        <v>3.49</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="15">
@@ -6389,24 +5399,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Mark Andrews</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TE9</t>
+          <t>TE16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TE13</t>
+          <t>TE16</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10.6</v>
+        <v>7.4</v>
       </c>
       <c r="F15" t="n">
-        <v>12.27</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -6417,7 +5427,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jaguars D/ST</t>
+          <t>49ers D/ST</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6427,70 +5437,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D/ST10</t>
+          <t>D/ST8</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>4.33</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D/ST</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chiefs D/ST</t>
+          <t>Cameron Dicker</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(n/a)</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>D/ST10</t>
+          <t>K32</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F17" t="n">
-        <v>5.21</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Eddy Pineiro</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>K18</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
   </sheetData>
